--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685655</v>
+        <v>122685648</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458267</v>
+        <v>458214</v>
       </c>
       <c r="R13" t="n">
-        <v>7071506</v>
+        <v>7071298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685648</v>
+        <v>122685640</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458214</v>
+        <v>457958</v>
       </c>
       <c r="R14" t="n">
-        <v>7071298</v>
+        <v>7071504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685640</v>
+        <v>122685655</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457958</v>
+        <v>458267</v>
       </c>
       <c r="R15" t="n">
-        <v>7071504</v>
+        <v>7071506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685656</v>
+        <v>122685641</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458204</v>
+        <v>458013</v>
       </c>
       <c r="R2" t="n">
-        <v>7071515</v>
+        <v>7071532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685646</v>
+        <v>122685642</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458076</v>
+        <v>458105</v>
       </c>
       <c r="R3" t="n">
-        <v>7071533</v>
+        <v>7071656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685642</v>
+        <v>122685654</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458105</v>
+        <v>458194</v>
       </c>
       <c r="R4" t="n">
-        <v>7071656</v>
+        <v>7071511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685654</v>
+        <v>122685653</v>
       </c>
       <c r="B5" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458194</v>
+        <v>458270</v>
       </c>
       <c r="R5" t="n">
-        <v>7071511</v>
+        <v>7071462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685647</v>
+        <v>122685656</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458207</v>
+        <v>458204</v>
       </c>
       <c r="R6" t="n">
-        <v>7071289</v>
+        <v>7071515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685657</v>
+        <v>122685643</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458040</v>
+        <v>458258</v>
       </c>
       <c r="R7" t="n">
-        <v>7071505</v>
+        <v>7071470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685652</v>
+        <v>122685657</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458266</v>
+        <v>458040</v>
       </c>
       <c r="R8" t="n">
-        <v>7071504</v>
+        <v>7071505</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685645</v>
+        <v>122685646</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458088</v>
+        <v>458076</v>
       </c>
       <c r="R9" t="n">
-        <v>7071543</v>
+        <v>7071533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685641</v>
+        <v>122685648</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458013</v>
+        <v>458214</v>
       </c>
       <c r="R10" t="n">
-        <v>7071532</v>
+        <v>7071298</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685643</v>
+        <v>122685645</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458258</v>
+        <v>458088</v>
       </c>
       <c r="R11" t="n">
-        <v>7071470</v>
+        <v>7071543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685653</v>
+        <v>122685655</v>
       </c>
       <c r="B12" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458270</v>
+        <v>458267</v>
       </c>
       <c r="R12" t="n">
-        <v>7071462</v>
+        <v>7071506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685648</v>
+        <v>122685644</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458214</v>
+        <v>458191</v>
       </c>
       <c r="R13" t="n">
-        <v>7071298</v>
+        <v>7071450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685640</v>
+        <v>122685652</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,7 +1989,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457958</v>
+        <v>458266</v>
       </c>
       <c r="R14" t="n">
         <v>7071504</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685655</v>
+        <v>122685647</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458267</v>
+        <v>458207</v>
       </c>
       <c r="R15" t="n">
-        <v>7071506</v>
+        <v>7071289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685644</v>
+        <v>122685640</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458191</v>
+        <v>457958</v>
       </c>
       <c r="R16" t="n">
-        <v>7071450</v>
+        <v>7071504</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685641</v>
+        <v>122685652</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458013</v>
+        <v>458266</v>
       </c>
       <c r="R2" t="n">
-        <v>7071532</v>
+        <v>7071504</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685642</v>
+        <v>122685641</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458105</v>
+        <v>458013</v>
       </c>
       <c r="R3" t="n">
-        <v>7071656</v>
+        <v>7071532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685654</v>
+        <v>122685657</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458194</v>
+        <v>458040</v>
       </c>
       <c r="R4" t="n">
-        <v>7071511</v>
+        <v>7071505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685653</v>
+        <v>122685655</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458270</v>
+        <v>458267</v>
       </c>
       <c r="R5" t="n">
-        <v>7071462</v>
+        <v>7071506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685656</v>
+        <v>122685643</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458204</v>
+        <v>458258</v>
       </c>
       <c r="R6" t="n">
-        <v>7071515</v>
+        <v>7071470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685643</v>
+        <v>122685653</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458258</v>
+        <v>458270</v>
       </c>
       <c r="R7" t="n">
-        <v>7071470</v>
+        <v>7071462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685657</v>
+        <v>122685656</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458040</v>
+        <v>458204</v>
       </c>
       <c r="R8" t="n">
-        <v>7071505</v>
+        <v>7071515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685646</v>
+        <v>122685645</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458076</v>
+        <v>458088</v>
       </c>
       <c r="R9" t="n">
-        <v>7071533</v>
+        <v>7071543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685648</v>
+        <v>122685644</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458214</v>
+        <v>458191</v>
       </c>
       <c r="R10" t="n">
-        <v>7071298</v>
+        <v>7071450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685645</v>
+        <v>122685647</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458088</v>
+        <v>458207</v>
       </c>
       <c r="R11" t="n">
-        <v>7071543</v>
+        <v>7071289</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685655</v>
+        <v>122685640</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458267</v>
+        <v>457958</v>
       </c>
       <c r="R12" t="n">
-        <v>7071506</v>
+        <v>7071504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685644</v>
+        <v>122685646</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458191</v>
+        <v>458076</v>
       </c>
       <c r="R13" t="n">
-        <v>7071450</v>
+        <v>7071533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685652</v>
+        <v>122685648</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458266</v>
+        <v>458214</v>
       </c>
       <c r="R14" t="n">
-        <v>7071504</v>
+        <v>7071298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685647</v>
+        <v>122685642</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458207</v>
+        <v>458105</v>
       </c>
       <c r="R15" t="n">
-        <v>7071289</v>
+        <v>7071656</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685640</v>
+        <v>122685654</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457958</v>
+        <v>458194</v>
       </c>
       <c r="R16" t="n">
-        <v>7071504</v>
+        <v>7071511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685652</v>
+        <v>122685646</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458266</v>
+        <v>458076</v>
       </c>
       <c r="R2" t="n">
-        <v>7071504</v>
+        <v>7071533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685641</v>
+        <v>122685655</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458013</v>
+        <v>458267</v>
       </c>
       <c r="R3" t="n">
-        <v>7071532</v>
+        <v>7071506</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685657</v>
+        <v>122685653</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458040</v>
+        <v>458270</v>
       </c>
       <c r="R4" t="n">
-        <v>7071505</v>
+        <v>7071462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685655</v>
+        <v>122685641</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458267</v>
+        <v>458013</v>
       </c>
       <c r="R5" t="n">
-        <v>7071506</v>
+        <v>7071532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685643</v>
+        <v>122685647</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458258</v>
+        <v>458207</v>
       </c>
       <c r="R6" t="n">
-        <v>7071470</v>
+        <v>7071289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685653</v>
+        <v>122685642</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458270</v>
+        <v>458105</v>
       </c>
       <c r="R7" t="n">
-        <v>7071462</v>
+        <v>7071656</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685656</v>
+        <v>122685645</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458204</v>
+        <v>458088</v>
       </c>
       <c r="R8" t="n">
-        <v>7071515</v>
+        <v>7071543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685645</v>
+        <v>122685656</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458088</v>
+        <v>458204</v>
       </c>
       <c r="R9" t="n">
-        <v>7071543</v>
+        <v>7071515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685644</v>
+        <v>122685654</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458191</v>
+        <v>458194</v>
       </c>
       <c r="R10" t="n">
-        <v>7071450</v>
+        <v>7071511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685647</v>
+        <v>122685657</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458207</v>
+        <v>458040</v>
       </c>
       <c r="R11" t="n">
-        <v>7071289</v>
+        <v>7071505</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685640</v>
+        <v>122685648</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457958</v>
+        <v>458214</v>
       </c>
       <c r="R12" t="n">
-        <v>7071504</v>
+        <v>7071298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685646</v>
+        <v>122685640</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458076</v>
+        <v>457958</v>
       </c>
       <c r="R13" t="n">
-        <v>7071533</v>
+        <v>7071504</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685648</v>
+        <v>122685643</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458214</v>
+        <v>458258</v>
       </c>
       <c r="R14" t="n">
-        <v>7071298</v>
+        <v>7071470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685642</v>
+        <v>122685652</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458105</v>
+        <v>458266</v>
       </c>
       <c r="R15" t="n">
-        <v>7071656</v>
+        <v>7071504</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685654</v>
+        <v>122685644</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458194</v>
+        <v>458191</v>
       </c>
       <c r="R16" t="n">
-        <v>7071511</v>
+        <v>7071450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685643</v>
+        <v>122685652</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458258</v>
+        <v>458266</v>
       </c>
       <c r="R14" t="n">
-        <v>7071470</v>
+        <v>7071504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685652</v>
+        <v>122685643</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458266</v>
+        <v>458258</v>
       </c>
       <c r="R15" t="n">
-        <v>7071504</v>
+        <v>7071470</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2127,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685646</v>
+        <v>122685644</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458076</v>
+        <v>458191</v>
       </c>
       <c r="R2" t="n">
-        <v>7071533</v>
+        <v>7071450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685655</v>
+        <v>122685653</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458267</v>
+        <v>458270</v>
       </c>
       <c r="R3" t="n">
-        <v>7071506</v>
+        <v>7071462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685653</v>
+        <v>122685645</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458270</v>
+        <v>458088</v>
       </c>
       <c r="R4" t="n">
-        <v>7071462</v>
+        <v>7071543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685641</v>
+        <v>122685648</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458013</v>
+        <v>458214</v>
       </c>
       <c r="R5" t="n">
-        <v>7071532</v>
+        <v>7071298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685647</v>
+        <v>122685642</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458207</v>
+        <v>458105</v>
       </c>
       <c r="R6" t="n">
-        <v>7071289</v>
+        <v>7071656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685642</v>
+        <v>122685643</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458105</v>
+        <v>458258</v>
       </c>
       <c r="R7" t="n">
-        <v>7071656</v>
+        <v>7071470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685645</v>
+        <v>122685655</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458088</v>
+        <v>458267</v>
       </c>
       <c r="R8" t="n">
-        <v>7071543</v>
+        <v>7071506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685656</v>
+        <v>122685652</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458204</v>
+        <v>458266</v>
       </c>
       <c r="R9" t="n">
-        <v>7071515</v>
+        <v>7071504</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685654</v>
+        <v>122685657</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458194</v>
+        <v>458040</v>
       </c>
       <c r="R10" t="n">
-        <v>7071511</v>
+        <v>7071505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685657</v>
+        <v>122685647</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458040</v>
+        <v>458207</v>
       </c>
       <c r="R11" t="n">
-        <v>7071505</v>
+        <v>7071289</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685648</v>
+        <v>122685641</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458214</v>
+        <v>458013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071298</v>
+        <v>7071532</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685652</v>
+        <v>122685656</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458266</v>
+        <v>458204</v>
       </c>
       <c r="R14" t="n">
-        <v>7071504</v>
+        <v>7071515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685643</v>
+        <v>122685646</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458258</v>
+        <v>458076</v>
       </c>
       <c r="R15" t="n">
-        <v>7071470</v>
+        <v>7071533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685644</v>
+        <v>122685654</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458191</v>
+        <v>458194</v>
       </c>
       <c r="R16" t="n">
-        <v>7071450</v>
+        <v>7071511</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685644</v>
+        <v>122685652</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458191</v>
+        <v>458266</v>
       </c>
       <c r="R2" t="n">
-        <v>7071450</v>
+        <v>7071504</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685653</v>
+        <v>122685641</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458270</v>
+        <v>458013</v>
       </c>
       <c r="R3" t="n">
-        <v>7071462</v>
+        <v>7071532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685645</v>
+        <v>122685647</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458088</v>
+        <v>458207</v>
       </c>
       <c r="R4" t="n">
-        <v>7071543</v>
+        <v>7071289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685648</v>
+        <v>122685642</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458214</v>
+        <v>458105</v>
       </c>
       <c r="R5" t="n">
-        <v>7071298</v>
+        <v>7071656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685642</v>
+        <v>122685653</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458105</v>
+        <v>458270</v>
       </c>
       <c r="R6" t="n">
-        <v>7071656</v>
+        <v>7071462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685643</v>
+        <v>122685657</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458258</v>
+        <v>458040</v>
       </c>
       <c r="R7" t="n">
-        <v>7071470</v>
+        <v>7071505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685655</v>
+        <v>122685654</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458267</v>
+        <v>458194</v>
       </c>
       <c r="R8" t="n">
-        <v>7071506</v>
+        <v>7071511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685652</v>
+        <v>122685655</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458266</v>
+        <v>458267</v>
       </c>
       <c r="R9" t="n">
-        <v>7071504</v>
+        <v>7071506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685657</v>
+        <v>122685646</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458040</v>
+        <v>458076</v>
       </c>
       <c r="R10" t="n">
-        <v>7071505</v>
+        <v>7071533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685647</v>
+        <v>122685643</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458207</v>
+        <v>458258</v>
       </c>
       <c r="R11" t="n">
-        <v>7071289</v>
+        <v>7071470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685641</v>
+        <v>122685645</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458013</v>
+        <v>458088</v>
       </c>
       <c r="R12" t="n">
-        <v>7071532</v>
+        <v>7071543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685656</v>
+        <v>122685644</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458204</v>
+        <v>458191</v>
       </c>
       <c r="R14" t="n">
-        <v>7071515</v>
+        <v>7071450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685646</v>
+        <v>122685656</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458076</v>
+        <v>458204</v>
       </c>
       <c r="R15" t="n">
-        <v>7071533</v>
+        <v>7071515</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685654</v>
+        <v>122685648</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458194</v>
+        <v>458214</v>
       </c>
       <c r="R16" t="n">
-        <v>7071511</v>
+        <v>7071298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -1837,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685640</v>
+        <v>122685644</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457958</v>
+        <v>458191</v>
       </c>
       <c r="R13" t="n">
-        <v>7071504</v>
+        <v>7071450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685644</v>
+        <v>122685656</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458191</v>
+        <v>458204</v>
       </c>
       <c r="R14" t="n">
-        <v>7071450</v>
+        <v>7071515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685656</v>
+        <v>122685640</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458204</v>
+        <v>457958</v>
       </c>
       <c r="R15" t="n">
-        <v>7071515</v>
+        <v>7071504</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685652</v>
+        <v>122685653</v>
       </c>
       <c r="B2" t="n">
         <v>90970</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458266</v>
+        <v>458270</v>
       </c>
       <c r="R2" t="n">
-        <v>7071504</v>
+        <v>7071462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685641</v>
+        <v>122685657</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458013</v>
+        <v>458040</v>
       </c>
       <c r="R3" t="n">
-        <v>7071532</v>
+        <v>7071505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685647</v>
+        <v>122685645</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458207</v>
+        <v>458088</v>
       </c>
       <c r="R4" t="n">
-        <v>7071289</v>
+        <v>7071543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685642</v>
+        <v>122685641</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458105</v>
+        <v>458013</v>
       </c>
       <c r="R5" t="n">
-        <v>7071656</v>
+        <v>7071532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685653</v>
+        <v>122685652</v>
       </c>
       <c r="B6" t="n">
         <v>90970</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458270</v>
+        <v>458266</v>
       </c>
       <c r="R6" t="n">
-        <v>7071462</v>
+        <v>7071504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685657</v>
+        <v>122685643</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458040</v>
+        <v>458258</v>
       </c>
       <c r="R7" t="n">
-        <v>7071505</v>
+        <v>7071470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685654</v>
+        <v>122685648</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458194</v>
+        <v>458214</v>
       </c>
       <c r="R8" t="n">
-        <v>7071511</v>
+        <v>7071298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685655</v>
+        <v>122685654</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458267</v>
+        <v>458194</v>
       </c>
       <c r="R9" t="n">
-        <v>7071506</v>
+        <v>7071511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685643</v>
+        <v>122685647</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458258</v>
+        <v>458207</v>
       </c>
       <c r="R11" t="n">
-        <v>7071470</v>
+        <v>7071289</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685645</v>
+        <v>122685656</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458088</v>
+        <v>458204</v>
       </c>
       <c r="R12" t="n">
-        <v>7071543</v>
+        <v>7071515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685644</v>
+        <v>122685655</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458191</v>
+        <v>458267</v>
       </c>
       <c r="R13" t="n">
-        <v>7071450</v>
+        <v>7071506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685656</v>
+        <v>122685640</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458204</v>
+        <v>457958</v>
       </c>
       <c r="R14" t="n">
-        <v>7071515</v>
+        <v>7071504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685640</v>
+        <v>122685644</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457958</v>
+        <v>458191</v>
       </c>
       <c r="R15" t="n">
-        <v>7071504</v>
+        <v>7071450</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685648</v>
+        <v>122685642</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458214</v>
+        <v>458105</v>
       </c>
       <c r="R16" t="n">
-        <v>7071298</v>
+        <v>7071656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685653</v>
+        <v>122685657</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458270</v>
+        <v>458040</v>
       </c>
       <c r="R2" t="n">
-        <v>7071462</v>
+        <v>7071505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685657</v>
+        <v>122685644</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458040</v>
+        <v>458191</v>
       </c>
       <c r="R3" t="n">
-        <v>7071505</v>
+        <v>7071450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685645</v>
+        <v>122685640</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458088</v>
+        <v>457958</v>
       </c>
       <c r="R4" t="n">
-        <v>7071543</v>
+        <v>7071504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685641</v>
+        <v>122685648</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458013</v>
+        <v>458214</v>
       </c>
       <c r="R5" t="n">
-        <v>7071532</v>
+        <v>7071298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685652</v>
+        <v>122685656</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458266</v>
+        <v>458204</v>
       </c>
       <c r="R6" t="n">
-        <v>7071504</v>
+        <v>7071515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685648</v>
+        <v>122685654</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458214</v>
+        <v>458194</v>
       </c>
       <c r="R8" t="n">
-        <v>7071298</v>
+        <v>7071511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685654</v>
+        <v>122685653</v>
       </c>
       <c r="B9" t="n">
         <v>90970</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458194</v>
+        <v>458270</v>
       </c>
       <c r="R9" t="n">
-        <v>7071511</v>
+        <v>7071462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685646</v>
+        <v>122685647</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458076</v>
+        <v>458207</v>
       </c>
       <c r="R10" t="n">
-        <v>7071533</v>
+        <v>7071289</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685647</v>
+        <v>122685655</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458207</v>
+        <v>458267</v>
       </c>
       <c r="R11" t="n">
-        <v>7071289</v>
+        <v>7071506</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685656</v>
+        <v>122685646</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458204</v>
+        <v>458076</v>
       </c>
       <c r="R12" t="n">
-        <v>7071515</v>
+        <v>7071533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685655</v>
+        <v>122685642</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458267</v>
+        <v>458105</v>
       </c>
       <c r="R13" t="n">
-        <v>7071506</v>
+        <v>7071656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685640</v>
+        <v>122685652</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,7 +1989,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457958</v>
+        <v>458266</v>
       </c>
       <c r="R14" t="n">
         <v>7071504</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685644</v>
+        <v>122685641</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458191</v>
+        <v>458013</v>
       </c>
       <c r="R15" t="n">
-        <v>7071450</v>
+        <v>7071532</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685642</v>
+        <v>122685645</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458105</v>
+        <v>458088</v>
       </c>
       <c r="R16" t="n">
-        <v>7071656</v>
+        <v>7071543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122685657</v>
+        <v>122685656</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458040</v>
+        <v>458204</v>
       </c>
       <c r="R2" t="n">
-        <v>7071505</v>
+        <v>7071515</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122685644</v>
+        <v>122685643</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458191</v>
+        <v>458258</v>
       </c>
       <c r="R3" t="n">
-        <v>7071450</v>
+        <v>7071470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685640</v>
+        <v>122685655</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457958</v>
+        <v>458267</v>
       </c>
       <c r="R4" t="n">
-        <v>7071504</v>
+        <v>7071506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122685656</v>
+        <v>122685645</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458204</v>
+        <v>458088</v>
       </c>
       <c r="R6" t="n">
-        <v>7071515</v>
+        <v>7071543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122685643</v>
+        <v>122685653</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458258</v>
+        <v>458270</v>
       </c>
       <c r="R7" t="n">
-        <v>7071470</v>
+        <v>7071462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122685654</v>
+        <v>122685657</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458194</v>
+        <v>458040</v>
       </c>
       <c r="R8" t="n">
-        <v>7071511</v>
+        <v>7071505</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122685653</v>
+        <v>122685647</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458270</v>
+        <v>458207</v>
       </c>
       <c r="R9" t="n">
-        <v>7071462</v>
+        <v>7071289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122685647</v>
+        <v>122685644</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458207</v>
+        <v>458191</v>
       </c>
       <c r="R10" t="n">
-        <v>7071289</v>
+        <v>7071450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685655</v>
+        <v>122685652</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458267</v>
+        <v>458266</v>
       </c>
       <c r="R11" t="n">
-        <v>7071506</v>
+        <v>7071504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685646</v>
+        <v>122685642</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458076</v>
+        <v>458105</v>
       </c>
       <c r="R12" t="n">
-        <v>7071533</v>
+        <v>7071656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122685642</v>
+        <v>122685640</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458105</v>
+        <v>457958</v>
       </c>
       <c r="R13" t="n">
-        <v>7071656</v>
+        <v>7071504</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685652</v>
+        <v>122685654</v>
       </c>
       <c r="B14" t="n">
         <v>90970</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458266</v>
+        <v>458194</v>
       </c>
       <c r="R14" t="n">
-        <v>7071504</v>
+        <v>7071511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685641</v>
+        <v>122685646</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458013</v>
+        <v>458076</v>
       </c>
       <c r="R15" t="n">
-        <v>7071532</v>
+        <v>7071533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122685645</v>
+        <v>122685641</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458088</v>
+        <v>458013</v>
       </c>
       <c r="R16" t="n">
-        <v>7071543</v>
+        <v>7071532</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122685655</v>
+        <v>122685648</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458267</v>
+        <v>458214</v>
       </c>
       <c r="R4" t="n">
-        <v>7071506</v>
+        <v>7071298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122685648</v>
+        <v>122685655</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458214</v>
+        <v>458267</v>
       </c>
       <c r="R5" t="n">
-        <v>7071298</v>
+        <v>7071506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122685652</v>
+        <v>122685642</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458266</v>
+        <v>458105</v>
       </c>
       <c r="R11" t="n">
-        <v>7071504</v>
+        <v>7071656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122685642</v>
+        <v>122685652</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458105</v>
+        <v>458266</v>
       </c>
       <c r="R12" t="n">
-        <v>7071656</v>
+        <v>7071504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122685654</v>
+        <v>122685646</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458194</v>
+        <v>458076</v>
       </c>
       <c r="R14" t="n">
-        <v>7071511</v>
+        <v>7071533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122685646</v>
+        <v>122685654</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458076</v>
+        <v>458194</v>
       </c>
       <c r="R15" t="n">
-        <v>7071533</v>
+        <v>7071511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,6 +2263,560 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123749378</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91001</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>458147</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7071169</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123752392</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>458095</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7071521</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ska mikras. I grannaturskog med väldigt rikliga förekomster av granticka.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Död granticka</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Död granticka</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123747930</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>457805</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7071313</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123752396</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91001</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>458095</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7071521</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123748826</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74880</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>458233</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071295</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123752392</v>
+        <v>123747930</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>74875</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,41 +2384,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2063</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458095</v>
+        <v>457805</v>
       </c>
       <c r="R18" t="n">
-        <v>7071521</v>
+        <v>7071313</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2453,34 +2450,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ska mikras. I grannaturskog med väldigt rikliga förekomster av granticka.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
           <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Död granticka</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Död granticka</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2498,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123747930</v>
+        <v>123752396</v>
       </c>
       <c r="B19" t="n">
-        <v>74875</v>
+        <v>91001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,34 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457805</v>
+        <v>458095</v>
       </c>
       <c r="R19" t="n">
-        <v>7071313</v>
+        <v>7071521</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2605,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123752396</v>
+        <v>123748826</v>
       </c>
       <c r="B20" t="n">
-        <v>91001</v>
+        <v>74880</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458095</v>
+        <v>458233</v>
       </c>
       <c r="R20" t="n">
-        <v>7071521</v>
+        <v>7071295</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2712,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123748826</v>
+        <v>123752392</v>
       </c>
       <c r="B21" t="n">
-        <v>74880</v>
+        <v>91334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,38 +2705,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>2063</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458233</v>
+        <v>458095</v>
       </c>
       <c r="R21" t="n">
-        <v>7071295</v>
+        <v>7071521</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2796,12 +2780,23 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
           <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Död granticka</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Död granticka</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123749378</v>
+        <v>123748826</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>74883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458147</v>
+        <v>458233</v>
       </c>
       <c r="R17" t="n">
-        <v>7071169</v>
+        <v>7071295</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123747930</v>
+        <v>123749378</v>
       </c>
       <c r="B18" t="n">
-        <v>74875</v>
+        <v>91006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457805</v>
+        <v>458147</v>
       </c>
       <c r="R18" t="n">
-        <v>7071313</v>
+        <v>7071169</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2482,7 +2482,7 @@
         <v>123752396</v>
       </c>
       <c r="B19" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123748826</v>
+        <v>123747930</v>
       </c>
       <c r="B20" t="n">
-        <v>74880</v>
+        <v>74878</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,34 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458233</v>
+        <v>457805</v>
       </c>
       <c r="R20" t="n">
-        <v>7071295</v>
+        <v>7071313</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,7 +2696,7 @@
         <v>123752392</v>
       </c>
       <c r="B21" t="n">
-        <v>91334</v>
+        <v>91339</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123748826</v>
+        <v>123749378</v>
       </c>
       <c r="B17" t="n">
-        <v>74883</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458233</v>
+        <v>458147</v>
       </c>
       <c r="R17" t="n">
-        <v>7071295</v>
+        <v>7071169</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123749378</v>
+        <v>123747930</v>
       </c>
       <c r="B18" t="n">
-        <v>91006</v>
+        <v>74879</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458147</v>
+        <v>457805</v>
       </c>
       <c r="R18" t="n">
-        <v>7071169</v>
+        <v>7071313</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2482,7 +2482,7 @@
         <v>123752396</v>
       </c>
       <c r="B19" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123747930</v>
+        <v>123748826</v>
       </c>
       <c r="B20" t="n">
-        <v>74878</v>
+        <v>74884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,34 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457805</v>
+        <v>458233</v>
       </c>
       <c r="R20" t="n">
-        <v>7071313</v>
+        <v>7071295</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,7 +2696,7 @@
         <v>123752392</v>
       </c>
       <c r="B21" t="n">
-        <v>91339</v>
+        <v>91341</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123749378</v>
+        <v>123748826</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>74884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458147</v>
+        <v>458233</v>
       </c>
       <c r="R17" t="n">
-        <v>7071169</v>
+        <v>7071295</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123747930</v>
+        <v>123749378</v>
       </c>
       <c r="B18" t="n">
-        <v>74879</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457805</v>
+        <v>458147</v>
       </c>
       <c r="R18" t="n">
-        <v>7071313</v>
+        <v>7071169</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123752396</v>
+        <v>123747930</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>74879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458095</v>
+        <v>457805</v>
       </c>
       <c r="R19" t="n">
-        <v>7071521</v>
+        <v>7071313</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123748826</v>
+        <v>123752396</v>
       </c>
       <c r="B20" t="n">
-        <v>74884</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458233</v>
+        <v>458095</v>
       </c>
       <c r="R20" t="n">
-        <v>7071295</v>
+        <v>7071521</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123748826</v>
+        <v>123747930</v>
       </c>
       <c r="B17" t="n">
-        <v>74884</v>
+        <v>74879</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458233</v>
+        <v>457805</v>
       </c>
       <c r="R17" t="n">
-        <v>7071295</v>
+        <v>7071313</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123749378</v>
+        <v>123748826</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>74884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458147</v>
+        <v>458233</v>
       </c>
       <c r="R18" t="n">
-        <v>7071169</v>
+        <v>7071295</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123747930</v>
+        <v>123752396</v>
       </c>
       <c r="B19" t="n">
-        <v>74879</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457805</v>
+        <v>458095</v>
       </c>
       <c r="R19" t="n">
-        <v>7071313</v>
+        <v>7071521</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123752396</v>
+        <v>123749378</v>
       </c>
       <c r="B20" t="n">
         <v>91008</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458095</v>
+        <v>458147</v>
       </c>
       <c r="R20" t="n">
-        <v>7071521</v>
+        <v>7071169</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123747930</v>
+        <v>123748826</v>
       </c>
       <c r="B17" t="n">
-        <v>74879</v>
+        <v>74884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457805</v>
+        <v>458233</v>
       </c>
       <c r="R17" t="n">
-        <v>7071313</v>
+        <v>7071295</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123748826</v>
+        <v>123749378</v>
       </c>
       <c r="B18" t="n">
-        <v>74884</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458233</v>
+        <v>458147</v>
       </c>
       <c r="R18" t="n">
-        <v>7071295</v>
+        <v>7071169</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123749378</v>
+        <v>123747930</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>74879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,34 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458147</v>
+        <v>457805</v>
       </c>
       <c r="R20" t="n">
-        <v>7071169</v>
+        <v>7071313</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123748826</v>
+        <v>123749378</v>
       </c>
       <c r="B17" t="n">
-        <v>74884</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458233</v>
+        <v>458147</v>
       </c>
       <c r="R17" t="n">
-        <v>7071295</v>
+        <v>7071169</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123749378</v>
+        <v>123752396</v>
       </c>
       <c r="B18" t="n">
         <v>91008</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458147</v>
+        <v>458095</v>
       </c>
       <c r="R18" t="n">
-        <v>7071169</v>
+        <v>7071521</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123752396</v>
+        <v>123747930</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>74879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458095</v>
+        <v>457805</v>
       </c>
       <c r="R19" t="n">
-        <v>7071521</v>
+        <v>7071313</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123747930</v>
+        <v>123748826</v>
       </c>
       <c r="B20" t="n">
-        <v>74879</v>
+        <v>74884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,34 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457805</v>
+        <v>458233</v>
       </c>
       <c r="R20" t="n">
-        <v>7071313</v>
+        <v>7071295</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123752396</v>
+        <v>123748826</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>74884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458095</v>
+        <v>458233</v>
       </c>
       <c r="R18" t="n">
-        <v>7071521</v>
+        <v>7071295</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123748826</v>
+        <v>123752396</v>
       </c>
       <c r="B20" t="n">
-        <v>74884</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458233</v>
+        <v>458095</v>
       </c>
       <c r="R20" t="n">
-        <v>7071295</v>
+        <v>7071521</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 54973-2024 artfynd.xlsx
+++ b/artfynd/A 54973-2024 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123747930</v>
+        <v>123752396</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bäckdalen, Bäckdalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457805</v>
+        <v>458095</v>
       </c>
       <c r="R17" t="n">
-        <v>7071313</v>
+        <v>7071521</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123749378</v>
+        <v>123747930</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckdalen, Bäckdalen, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458147</v>
+        <v>457805</v>
       </c>
       <c r="R18" t="n">
-        <v>7071169</v>
+        <v>7071313</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123752396</v>
+        <v>123749378</v>
       </c>
       <c r="B20" t="n">
         <v>91030</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458095</v>
+        <v>458147</v>
       </c>
       <c r="R20" t="n">
-        <v>7071521</v>
+        <v>7071169</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
